--- a/data/trans_dic/P8_1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P8_1_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 13,21</t>
+          <t>8,37; 13,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,73; 17,95</t>
+          <t>12,67; 18,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,93; 18,65</t>
+          <t>12,77; 18,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,33</t>
+          <t>13,67; 19,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 23,68</t>
+          <t>18,05; 24,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,33; 31,13</t>
+          <t>24,14; 30,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,33; 30,34</t>
+          <t>23,27; 30,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 23,9</t>
+          <t>16,69; 23,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,9; 17,79</t>
+          <t>13,82; 17,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 23,59</t>
+          <t>19,28; 23,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,99; 23,38</t>
+          <t>19,03; 23,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 20,98</t>
+          <t>16,72; 20,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,24; 13,45</t>
+          <t>9,24; 13,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,72; 18,68</t>
+          <t>13,67; 18,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,57; 17,13</t>
+          <t>12,64; 16,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 61,41</t>
+          <t>10,6; 65,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,73; 23,93</t>
+          <t>18,69; 24,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,83; 27,13</t>
+          <t>22,22; 27,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,74; 26,29</t>
+          <t>20,88; 26,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,8; 23,73</t>
+          <t>19,68; 23,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,74; 18,1</t>
+          <t>14,63; 18,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 22,28</t>
+          <t>18,59; 22,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,12; 20,88</t>
+          <t>17,35; 20,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 49,68</t>
+          <t>16,09; 50,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 14,89</t>
+          <t>9,94; 15,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,89</t>
+          <t>9,71; 15,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 15,62</t>
+          <t>10,67; 15,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 21,0</t>
+          <t>14,74; 20,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,5; 27,83</t>
+          <t>21,37; 27,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,63; 26,76</t>
+          <t>20,32; 27,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 24,13</t>
+          <t>17,87; 23,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 21,64</t>
+          <t>7,98; 21,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,35; 20,55</t>
+          <t>16,39; 20,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,87; 20,01</t>
+          <t>15,77; 19,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,02; 19,04</t>
+          <t>14,92; 18,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 19,72</t>
+          <t>11,52; 19,71</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 12,69</t>
+          <t>8,98; 12,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 17,19</t>
+          <t>12,3; 17,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 14,75</t>
+          <t>10,26; 14,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,59; 16,95</t>
+          <t>12,66; 17,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 22,76</t>
+          <t>17,43; 22,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 28,93</t>
+          <t>23,37; 28,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,21</t>
+          <t>17,66; 23,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,99; 25,09</t>
+          <t>18,24; 24,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 17,19</t>
+          <t>14,16; 17,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,87; 22,59</t>
+          <t>18,84; 22,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,06; 18,59</t>
+          <t>14,95; 18,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,47; 20,66</t>
+          <t>16,75; 20,46</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,22</t>
+          <t>10,08; 12,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 15,9</t>
+          <t>13,41; 15,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,78; 15,1</t>
+          <t>12,74; 15,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,31; 38,23</t>
+          <t>14,23; 37,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,0; 22,96</t>
+          <t>20,06; 22,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,87; 26,84</t>
+          <t>23,76; 26,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,13; 24,12</t>
+          <t>21,2; 24,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,68; 22,2</t>
+          <t>16,52; 22,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,49; 17,36</t>
+          <t>15,49; 17,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,16; 21,2</t>
+          <t>19,15; 21,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 19,36</t>
+          <t>17,37; 19,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 30,76</t>
+          <t>17,14; 29,77</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con limitación a hacer esfuerzos moderados</t>
+          <t>Población con limitación a hacer esfuerzos moderados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59341; 91706</t>
+          <t>58112; 90470</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89544; 126283</t>
+          <t>89157; 128562</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87274; 125862</t>
+          <t>86188; 122934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86848; 122812</t>
+          <t>86839; 124349</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>123377; 163002</t>
+          <t>124268; 165585</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>169595; 217017</t>
+          <t>168246; 215968</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>156950; 204129</t>
+          <t>156537; 203553</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>120752; 173355</t>
+          <t>121082; 172381</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>192214; 245874</t>
+          <t>190999; 242873</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266875; 330357</t>
+          <t>269955; 331897</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>255907; 315019</t>
+          <t>256511; 315160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>222418; 285478</t>
+          <t>227558; 285129</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88857; 129368</t>
+          <t>88915; 129541</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>139713; 190183</t>
+          <t>139142; 188336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>128519; 175167</t>
+          <t>129247; 173110</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125496; 732524</t>
+          <t>126431; 782551</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>181372; 231701</t>
+          <t>180947; 234368</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>225363; 280025</t>
+          <t>229385; 281553</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>216250; 274198</t>
+          <t>217779; 275495</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>189687; 227315</t>
+          <t>188575; 227637</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>284492; 349389</t>
+          <t>282310; 347452</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>379696; 456787</t>
+          <t>381034; 454443</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>353608; 431280</t>
+          <t>358245; 433585</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>349744; 1068557</t>
+          <t>346108; 1082614</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>67453; 101058</t>
+          <t>67429; 103696</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74180; 112818</t>
+          <t>73534; 114433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80065; 118642</t>
+          <t>81026; 117584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104749; 147963</t>
+          <t>103837; 145428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>147021; 190336</t>
+          <t>146150; 190807</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>160326; 207938</t>
+          <t>157952; 210460</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>140308; 189390</t>
+          <t>140315; 187677</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79173; 201976</t>
+          <t>74458; 200328</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>222768; 279910</t>
+          <t>223339; 277572</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>243565; 307071</t>
+          <t>242088; 304327</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>232038; 294136</t>
+          <t>230475; 292169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>189798; 322960</t>
+          <t>188751; 322840</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>83067; 119578</t>
+          <t>84632; 121121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117314; 162937</t>
+          <t>116581; 164418</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98099; 138261</t>
+          <t>96230; 136207</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>116709; 157081</t>
+          <t>117342; 158955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>184331; 236428</t>
+          <t>181038; 234898</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>247123; 304363</t>
+          <t>245848; 303265</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>189898; 242210</t>
+          <t>184285; 242438</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>197019; 274765</t>
+          <t>199667; 273581</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>276775; 340499</t>
+          <t>280404; 341476</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>377403; 451731</t>
+          <t>376828; 448766</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>298437; 368388</t>
+          <t>296277; 367252</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>333065; 417753</t>
+          <t>338593; 413720</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>333464; 400371</t>
+          <t>330433; 400334</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>459556; 544870</t>
+          <t>459374; 545048</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>433884; 512592</t>
+          <t>432584; 517136</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>494994; 1322586</t>
+          <t>492165; 1307074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>675730; 775730</t>
+          <t>677917; 773902</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>849247; 954911</t>
+          <t>845311; 949794</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>748953; 855052</t>
+          <t>751578; 854512</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>619280; 823824</t>
+          <t>613111; 827942</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1030860; 1155726</t>
+          <t>1030826; 1145216</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1338548; 1480716</t>
+          <t>1337813; 1471272</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1211092; 1343531</t>
+          <t>1205297; 1339200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1228718; 2206264</t>
+          <t>1229176; 2134927</t>
         </is>
       </c>
     </row>
